--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.82187355548893</v>
+        <v>3.383554452766951</v>
       </c>
       <c r="D2" t="n">
-        <v>20.69084392158336</v>
+        <v>3.362262137257297</v>
       </c>
       <c r="E2" t="n">
-        <v>5.702787376010935</v>
+        <v>0.926702948601777</v>
       </c>
       <c r="F2" t="n">
-        <v>5.744188805653163</v>
+        <v>0.9334306809186389</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.60884700821628</v>
+        <v>5.948937638835146</v>
       </c>
       <c r="D3" t="n">
-        <v>36.40309496714622</v>
+        <v>5.915502932161262</v>
       </c>
       <c r="E3" t="n">
-        <v>5.702787376010935</v>
+        <v>0.926702948601777</v>
       </c>
       <c r="F3" t="n">
-        <v>5.744188805653163</v>
+        <v>0.9334306809186389</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.08324166678824</v>
+        <v>4.563526770853089</v>
       </c>
       <c r="D4" t="n">
-        <v>27.87004836207479</v>
+        <v>4.528882858837154</v>
       </c>
       <c r="E4" t="n">
-        <v>5.702787376010935</v>
+        <v>0.926702948601777</v>
       </c>
       <c r="F4" t="n">
-        <v>5.744188805653163</v>
+        <v>0.9334306809186389</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.53718774346571</v>
+        <v>3.499793008313178</v>
       </c>
       <c r="D5" t="n">
-        <v>21.4985256756202</v>
+        <v>3.493510422288282</v>
       </c>
       <c r="E5" t="n">
-        <v>5.702787376010935</v>
+        <v>0.926702948601777</v>
       </c>
       <c r="F5" t="n">
-        <v>5.744188805653163</v>
+        <v>0.9334306809186389</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.40089781750965</v>
+        <v>4.940145895345318</v>
       </c>
       <c r="D6" t="n">
-        <v>30.54445488390395</v>
+        <v>4.963473918634391</v>
       </c>
       <c r="E6" t="n">
-        <v>5.702787376010935</v>
+        <v>0.926702948601777</v>
       </c>
       <c r="F6" t="n">
-        <v>5.744188805653163</v>
+        <v>0.9334306809186389</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.45367298187172</v>
+        <v>5.436221859554155</v>
       </c>
       <c r="D7" t="n">
-        <v>33.57411178997038</v>
+        <v>5.455793165870187</v>
       </c>
       <c r="E7" t="n">
-        <v>5.702787376010935</v>
+        <v>0.926702948601777</v>
       </c>
       <c r="F7" t="n">
-        <v>5.744188805653163</v>
+        <v>0.9334306809186389</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.0066879426581</v>
+        <v>5.526086790681942</v>
       </c>
       <c r="D8" t="n">
-        <v>34.1674015747771</v>
+        <v>5.552202755901278</v>
       </c>
       <c r="E8" t="n">
-        <v>5.702787376010935</v>
+        <v>0.926702948601777</v>
       </c>
       <c r="F8" t="n">
-        <v>5.744188805653163</v>
+        <v>0.9334306809186389</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
